--- a/clubs.xlsx
+++ b/clubs.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="175">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -88,7 +88,7 @@
     <t xml:space="preserve">EdwardsChurch.txt</t>
   </si>
   <si>
-    <t xml:space="preserve">A2</t>
+    <t xml:space="preserve">A</t>
   </si>
   <si>
     <t xml:space="preserve">Ankeny Squares</t>
@@ -97,7 +97,7 @@
     <t xml:space="preserve">ankenysquares.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">ankenysquares.com</t>
+    <t xml:space="preserve">https://www.ankenysquares.com/</t>
   </si>
   <si>
     <t xml:space="preserve">St. Paul Lutheran</t>
@@ -145,6 +145,9 @@
     <t xml:space="preserve">Circlesquareb.png</t>
   </si>
   <si>
+    <t xml:space="preserve">https://circle-square-b.mailchimpsites.com/</t>
+  </si>
+  <si>
     <t xml:space="preserve">IOOF Hall</t>
   </si>
   <si>
@@ -169,6 +172,9 @@
     <t xml:space="preserve">circulators.png</t>
   </si>
   <si>
+    <t xml:space="preserve">http://iowasquaredance.net/circulators/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cedar Falls Rec Center</t>
   </si>
   <si>
@@ -229,6 +235,33 @@
     <t xml:space="preserve">Guests $10</t>
   </si>
   <si>
+    <t xml:space="preserve">Heartland Singles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heartland.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.squaredancene.org/clubs/heartland/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rockbrook Methodist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9855 West Center Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2338682,-96.0689638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MR</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lads &amp; Lassies</t>
   </si>
   <si>
@@ -259,6 +292,54 @@
     <t xml:space="preserve">Marion County Campground</t>
   </si>
   <si>
+    <t xml:space="preserve">Loess Hills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LoessHills.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.squaredancene.org/clubs/loess/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Parlor</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">116 S. 6</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> St.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Missouri Valley,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.555797,-95.8874193</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maysville Wranglers</t>
   </si>
   <si>
@@ -286,6 +367,9 @@
     <t xml:space="preserve">MerryRounders.jpeg</t>
   </si>
   <si>
+    <t xml:space="preserve">http://iowasquaredance.net/merry-rounders-round-dance-club/</t>
+  </si>
+  <si>
     <t xml:space="preserve">R</t>
   </si>
   <si>
@@ -419,6 +503,48 @@
   </si>
   <si>
     <t xml:space="preserve">41.5459621,-90.6028968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stardusters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stardusters.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://iowasquaredance.net/stardusters/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith’s Dancing Meadows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1503 190th Street</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waverly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7739425,-92.457185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanglefoot Squares </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanglefoot.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.squaredancemissouri.com/Missouri/Club/Tanglefoot_Squares/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trinity United Methodist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224 South Main Street</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brookfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7820854,-93.0755355</t>
   </si>
   <si>
     <t xml:space="preserve">Union Squares</t>
@@ -456,7 +582,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="hh:mm\ AM/PM"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -477,6 +603,20 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -521,7 +661,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -531,6 +671,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -665,7 +809,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N202"/>
+  <dimension ref="A1:N206"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.71"/>
@@ -767,7 +911,7 @@
       <c r="B3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -843,61 +987,67 @@
       <c r="A5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="C5" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="D5" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>45</v>
       </c>
+      <c r="J5" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="K5" s="2" t="n">
-        <v>0.791666666666667</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.895833333333333</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0.583333333333333</v>
@@ -911,28 +1061,28 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="3" t="s">
         <v>58</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>59</v>
+      <c r="H7" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0.791666666666667</v>
@@ -946,28 +1096,28 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0.791666666666667</v>
@@ -976,243 +1126,243 @@
         <v>0.895833333333333</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>69</v>
+      <c r="A9" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="D9" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.791666666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0.895833333333333</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>69</v>
+      <c r="A10" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>81</v>
+      </c>
+      <c r="C10" s="4"/>
       <c r="D10" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="3"/>
+        <v>82</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>83</v>
+      </c>
       <c r="F10" s="1" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="2"/>
+      <c r="H10" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0.895833333333333</v>
+      </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>79</v>
+      <c r="A11" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>88</v>
+      </c>
+      <c r="C11" s="4"/>
       <c r="D11" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>82</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="E11" s="4"/>
       <c r="F11" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="2" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0.895833333333333</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="2"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>86</v>
+      <c r="A12" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>17</v>
+        <v>93</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="H12" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="4"/>
       <c r="K12" s="2" t="n">
         <v>0.791666666666667</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>88</v>
-      </c>
+        <v>0.895833333333333</v>
+      </c>
+      <c r="M12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>89</v>
+      <c r="A13" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>96</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="J13" s="4"/>
       <c r="K13" s="2" t="n">
-        <v>0.583333333333333</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0.6875</v>
+        <v>0.895833333333333</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>98</v>
+      <c r="A14" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J14" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="K14" s="2" t="n">
         <v>0.791666666666667</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0.895833333333333</v>
-      </c>
-      <c r="M14" s="1"/>
+        <v>0.875</v>
+      </c>
       <c r="N14" s="1" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>105</v>
+      <c r="A15" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F15" s="3" t="s">
         <v>109</v>
       </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="G15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0.583333333333333</v>
@@ -1222,71 +1372,70 @@
       </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>112</v>
+      <c r="A16" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>119</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J16" s="4"/>
       <c r="K16" s="2" t="n">
-        <v>0.666666666666667</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0.75</v>
-      </c>
+        <v>0.895833333333333</v>
+      </c>
+      <c r="M16" s="1"/>
       <c r="N16" s="1" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="F17" s="1" t="s">
         <v>125</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>127</v>
+      <c r="H17" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0.583333333333333</v>
@@ -1294,67 +1443,73 @@
       <c r="L17" s="2" t="n">
         <v>0.6875</v>
       </c>
+      <c r="M17" s="1"/>
       <c r="N17" s="1" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>18</v>
+        <v>136</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.791666666666667</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.895833333333333</v>
+        <v>0.75</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>32</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>133</v>
+      <c r="A19" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>138</v>
+      <c r="H19" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0.583333333333333</v>
@@ -1363,21 +1518,21 @@
         <v>0.6875</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>149</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>17</v>
+        <v>150</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>18</v>
@@ -1386,10 +1541,7 @@
         <v>19</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0.791666666666667</v>
@@ -1402,20 +1554,142 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
+      <c r="A21" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0.895833333333333</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
+      <c r="A22" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0.895833333333333</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
+      <c r="A23" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
+      <c r="A24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0.895833333333333</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K25" s="2"/>
@@ -2129,7 +2403,26 @@
       <c r="K202" s="2"/>
       <c r="L202" s="2"/>
     </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K203" s="2"/>
+      <c r="L203" s="2"/>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K204" s="2"/>
+      <c r="L204" s="2"/>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K205" s="2"/>
+      <c r="L205" s="2"/>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K206" s="2"/>
+      <c r="L206" s="2"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" display="https://www.ankenysquares.com/"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
